--- a/ArduinoIDE/_Project/SelfDrivingCar/CarModule/maps.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/CarModule/maps.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\CarModule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F35EEE-3B09-4827-81E8-3510B8A8F4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7D5E7E-48B0-45BA-821B-31736BCD87C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="GPS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>(0,0)</t>
   </si>
@@ -183,15 +184,150 @@
   <si>
     <t>(3,5)</t>
   </si>
+  <si>
+    <t>GPS座標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(X2,Y2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(X1+(X2-X1)/5),Y1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X1,Y1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X1,(Y1+(Y2-Y1)/3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="General&quot;m&quot;"/>
+    <numFmt numFmtId="187" formatCode="0.0000000000000"/>
+    <numFmt numFmtId="189" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="191" formatCode="0.000000000000000_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -226,6 +362,54 @@
     <font>
       <sz val="12"/>
       <color theme="9" tint="-0.249977111117893"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="4"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
@@ -311,7 +495,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -367,34 +551,37 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="191" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -736,13 +923,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.875" customWidth="1"/>
     <col min="2" max="6" width="5.625" customWidth="1"/>
     <col min="7" max="7" width="5.875" customWidth="1"/>
-    <col min="8" max="16" width="5.625" customWidth="1"/>
+    <col min="8" max="9" width="5.625" customWidth="1"/>
+    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1845,29 +2034,338 @@
         <v>36</v>
       </c>
     </row>
+    <row r="45" spans="1:17">
+      <c r="J45" s="19"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="J48" s="20"/>
+    </row>
+    <row r="49" spans="10:10">
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="10:10">
+      <c r="J50" s="20"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="J13:O16">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:F16">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>K13=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:F32">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>K29=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L29:O32">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>T29=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27292DF4-BBF0-48FD-AF98-588E17F9C7F6}">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="6.75" customWidth="1"/>
+    <col min="10" max="10" width="21.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="19"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="24">
+        <v>25.075442061456801</v>
+      </c>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="24">
+        <v>121.545006388793</v>
+      </c>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="24">
+        <v>25.073607005990301</v>
+      </c>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="24">
+        <v>121.548662194024</v>
+      </c>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="28.5">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" s="21" t="str">
+        <f>$B$2&amp;CHAR(10)&amp;$B$3</f>
+        <v>25.0754420614568
+121.545006388793</v>
+      </c>
+      <c r="C8" s="22" t="str">
+        <f>$B$2&amp;CHAR(10)&amp;($B$3+($B$5-$B$3)/5)</f>
+        <v>25.0754420614568
+121.545737549839</v>
+      </c>
+      <c r="D8" s="22" t="str">
+        <f>$B$2&amp;CHAR(10)&amp;($B$3+2*($B$5-$B$3)/5)</f>
+        <v>25.0754420614568
+121.546468710885</v>
+      </c>
+      <c r="E8" s="22" t="str">
+        <f>$B$2&amp;CHAR(10)&amp;($B$3+3*($B$5-$B$3)/5)</f>
+        <v>25.0754420614568
+121.547199871932</v>
+      </c>
+      <c r="F8" s="22" t="str">
+        <f>$B$2&amp;CHAR(10)&amp;($B$3+4*($B$5-$B$3)/5)</f>
+        <v>25.0754420614568
+121.547931032978</v>
+      </c>
+      <c r="G8" s="22" t="str">
+        <f>$B$2&amp;CHAR(10)&amp;($B$3+5*($B$5-$B$3)/5)</f>
+        <v>25.0754420614568
+121.548662194024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" s="22" t="str">
+        <f>($B$2+($B$4-$B$2)/3)&amp;CHAR(10)&amp;$B$3</f>
+        <v>25.0748303763013
+121.545006388793</v>
+      </c>
+      <c r="C9" s="22" t="str">
+        <f>($B$2+($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+($B$5-$B$3)/5)</f>
+        <v>25.0748303763013
+121.545737549839</v>
+      </c>
+      <c r="D9" s="22" t="str">
+        <f>($B$2+($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+2*($B$5-$B$3)/5)</f>
+        <v>25.0748303763013
+121.546468710885</v>
+      </c>
+      <c r="E9" s="22" t="str">
+        <f>($B$2+($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+3*($B$5-$B$3)/5)</f>
+        <v>25.0748303763013
+121.547199871932</v>
+      </c>
+      <c r="F9" s="22" t="str">
+        <f>($B$2+($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+4*($B$5-$B$3)/5)</f>
+        <v>25.0748303763013
+121.547931032978</v>
+      </c>
+      <c r="G9" s="22" t="str">
+        <f>($B$2+($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+5*($B$5-$B$3)/5)</f>
+        <v>25.0748303763013
+121.548662194024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" s="22" t="str">
+        <f>($B$2+2*($B$4-$B$2)/3)&amp;CHAR(10)&amp;$B$3</f>
+        <v>25.0742186911458
+121.545006388793</v>
+      </c>
+      <c r="C10" s="22" t="str">
+        <f>($B$2+2*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+($B$5-$B$3)/5)</f>
+        <v>25.0742186911458
+121.545737549839</v>
+      </c>
+      <c r="D10" s="22" t="str">
+        <f>($B$2+2*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+2*($B$5-$B$3)/5)</f>
+        <v>25.0742186911458
+121.546468710885</v>
+      </c>
+      <c r="E10" s="22" t="str">
+        <f>($B$2+2*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+3*($B$5-$B$3)/5)</f>
+        <v>25.0742186911458
+121.547199871932</v>
+      </c>
+      <c r="F10" s="22" t="str">
+        <f>($B$2+2*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+4*($B$5-$B$3)/5)</f>
+        <v>25.0742186911458
+121.547931032978</v>
+      </c>
+      <c r="G10" s="22" t="str">
+        <f>($B$2+2*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+5*($B$5-$B$3)/5)</f>
+        <v>25.0742186911458
+121.548662194024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" s="22" t="str">
+        <f>($B$2+3*($B$4-$B$2)/3)&amp;CHAR(10)&amp;$B$3</f>
+        <v>25.0736070059903
+121.545006388793</v>
+      </c>
+      <c r="C11" s="22" t="str">
+        <f>($B$2+3*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+($B$5-$B$3)/5)</f>
+        <v>25.0736070059903
+121.545737549839</v>
+      </c>
+      <c r="D11" s="22" t="str">
+        <f>($B$2+3*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+2*($B$5-$B$3)/5)</f>
+        <v>25.0736070059903
+121.546468710885</v>
+      </c>
+      <c r="E11" s="22" t="str">
+        <f>($B$2+3*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+3*($B$5-$B$3)/5)</f>
+        <v>25.0736070059903
+121.547199871932</v>
+      </c>
+      <c r="F11" s="22" t="str">
+        <f>($B$2+3*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+4*($B$5-$B$3)/5)</f>
+        <v>25.0736070059903
+121.547931032978</v>
+      </c>
+      <c r="G11" s="22" t="str">
+        <f>($B$2+3*($B$4-$B$2)/3)&amp;CHAR(10)&amp;($B$3+5*($B$5-$B$3)/5)</f>
+        <v>25.0736070059903
+121.548662194024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>